--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="169">
   <si>
     <t xml:space="preserve">do not print this form</t>
   </si>
@@ -121,7 +121,10 @@
     <t xml:space="preserve">R03</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce insemna continutul</t>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nu se aplica, dar este potrivit</t>
   </si>
   <si>
     <t xml:space="preserve">R04</t>
@@ -982,6 +985,12 @@
     <t xml:space="preserve">Tool used:</t>
   </si>
   <si>
+    <t xml:space="preserve">SonarQube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.03.2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">File, Line</t>
   </si>
   <si>
@@ -992,6 +1001,80 @@
   </si>
   <si>
     <t xml:space="preserve">After/Argument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FileAbstractRepository:9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID nu este de tip ^[A-Z][0-9]?$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consider ID ca este un nume bun pentru type parameter in acest caz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FileAbstractRepository:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unnecessary cast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return (List&lt;E&gt;)StreamSupport….</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return StreamSupport….</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FileAbstractRepository:23-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commented block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//            .collect(Collectors.toList());
+        // return (List&lt;E&gt;) entities.values();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am sters blocul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsvExporter:31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic exceptions should never be thrown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiar daca ideal ar fi folosirea unei librari pentru aplicatie curenta un simplu RuntimeException este aceptabila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsvExporter:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility classes should not have public constructors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">private CsvExporter() {
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsvExporter:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parentheses should be removed from a single lambda parameter when its type is inferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.filter((p1)-&gt;i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.filter(p1-&gt;i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsvExporter:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unnecessary imports should be removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am sters importul</t>
   </si>
   <si>
     <t xml:space="preserve">Effort to perform tool-based code analysis (hours):</t>
@@ -1005,7 +1088,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1140,6 +1223,24 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1232,100 +1333,100 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1333,39 +1434,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1624,16 +1749,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="41.5"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.51"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="8.83"/>
   </cols>
   <sheetData>
@@ -1725,7 +1850,7 @@
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
     </row>
-    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
         <v>17</v>
       </c>
@@ -1739,7 +1864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="30.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="n">
         <v>1</v>
       </c>
@@ -1753,7 +1878,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="n">
         <f aca="false">B10+1</f>
         <v>2</v>
@@ -1768,7 +1893,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="30.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="n">
         <f aca="false">B11+1</f>
         <v>3</v>
@@ -1783,7 +1908,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="n">
         <f aca="false">B12+1</f>
         <v>4</v>
@@ -1798,7 +1923,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="n">
         <f aca="false">B13+1</f>
         <v>5</v>
@@ -1813,7 +1938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="n">
         <f aca="false">B14+1</f>
         <v>6</v>
@@ -1826,7 +1951,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="n">
         <f aca="false">B15+1</f>
         <v>7</v>
@@ -1847,24 +1972,24 @@
       <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>7</v>
+      <c r="D17" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="30.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="n">
         <f aca="false">B17+1</f>
         <v>9</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1873,49 +1998,49 @@
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="n">
         <f aca="false">B19+1</f>
         <v>11</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="n">
         <f aca="false">B20+1</f>
         <v>12</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="n">
         <f aca="false">B21+1</f>
         <v>13</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1941,7 +2066,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="15" t="n">
@@ -1974,7 +2099,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.33"/>
@@ -1999,7 +2124,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2028,7 +2153,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" s="22"/>
       <c r="H4" s="6" t="s">
@@ -2043,7 +2168,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>11</v>
@@ -2088,33 +2213,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="n">
         <f aca="false">B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2123,43 +2248,43 @@
         <v>3</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="n">
         <f aca="false">B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="n">
         <f aca="false">B13+1</f>
         <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2168,13 +2293,13 @@
         <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2183,13 +2308,13 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2198,13 +2323,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2213,13 +2338,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2228,13 +2353,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2243,13 +2368,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2258,13 +2383,13 @@
         <v>12</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2273,13 +2398,13 @@
         <v>13</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2288,13 +2413,13 @@
         <v>14</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2303,13 +2428,13 @@
         <v>15</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2318,13 +2443,13 @@
         <v>16</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2333,18 +2458,18 @@
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="15"/>
@@ -2378,12 +2503,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="142.76"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26.67"/>
@@ -2403,7 +2528,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2432,7 +2557,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" s="29"/>
       <c r="H4" s="6" t="s">
@@ -2450,7 +2575,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" s="30"/>
       <c r="H5" s="6" t="s">
@@ -2469,7 +2594,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -2478,7 +2603,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="12"/>
     </row>
@@ -2496,63 +2621,63 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="n">
         <f aca="false">B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="n">
         <f aca="false">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="n">
         <f aca="false">B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2561,88 +2686,88 @@
         <v>5</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="n">
         <f aca="false">B14+1</f>
         <v>6</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="n">
         <f aca="false">B15+1</f>
         <v>7</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="n">
         <f aca="false">B16+1</f>
         <v>8</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="n">
         <f aca="false">B17+1</f>
         <v>9</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="n">
         <f aca="false">B18+1</f>
         <v>10</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,73 +2776,73 @@
         <v>11</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="n">
         <f aca="false">B20+1</f>
         <v>12</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="n">
         <f aca="false">B21+1</f>
         <v>13</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="n">
         <f aca="false">B22+1</f>
         <v>14</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="n">
         <f aca="false">B23+1</f>
         <v>15</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2776,7 +2901,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" s="20"/>
       <c r="E32" s="15" t="n">
@@ -2809,14 +2934,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44.39"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="8.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.83"/>
@@ -2835,7 +2960,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2861,9 +2986,11 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="29"/>
+        <v>137</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>138</v>
+      </c>
       <c r="E4" s="29"/>
       <c r="H4" s="6" t="s">
         <v>10</v>
@@ -2879,7 +3006,9 @@
       <c r="C5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="12"/>
       <c r="H5" s="6" t="s">
         <v>14</v>
@@ -2896,7 +3025,9 @@
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="12"/>
+      <c r="D6" s="12" t="s">
+        <v>139</v>
+      </c>
       <c r="E6" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2904,86 +3035,134 @@
         <v>17</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="31"/>
+      <c r="C10" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>145</v>
+      </c>
       <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
+      <c r="F10" s="32" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="n">
         <f aca="false">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="n">
         <f aca="false">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="n">
         <f aca="false">B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="31"/>
+      <c r="C13" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>156</v>
+      </c>
       <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="n">
         <f aca="false">B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="31"/>
+      <c r="C14" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>159</v>
+      </c>
       <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="35" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="n">
         <f aca="false">B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="n">
         <f aca="false">B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="31"/>
+      <c r="C16" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>166</v>
+      </c>
       <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="F16" s="18" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="n">
@@ -3126,12 +3305,14 @@
       <c r="F30" s="31"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="33"/>
+      <c r="C32" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39" t="n">
+        <v>0.25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
